--- a/Figures/Binomial GAM/LD5_Table.xlsx
+++ b/Figures/Binomial GAM/LD5_Table.xlsx
@@ -1,61 +1,86 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABerk\Documents\R\Github Repositories\phyto_synthesis\Figures\Binomial GAM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF07CA5-974E-4162-9CAA-88BDAE30E3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="20370" yWindow="-2940" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t xml:space="preserve">Parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LD_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">laglogDissAmmonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">laglogDissNitrateNitrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">laglogDissOrthophos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">laglogSAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logConductivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logDissAmmonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logDissNitrateNitrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logDissOrthophos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logSAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>DissAmmonia</t>
+  </si>
+  <si>
+    <t>Lag DissNitrateNitrite</t>
+  </si>
+  <si>
+    <t>Lag DissOrthophos</t>
+  </si>
+  <si>
+    <t>Lag SAC</t>
+  </si>
+  <si>
+    <t>Conductivity</t>
+  </si>
+  <si>
+    <t>DissNitrateNitrite</t>
+  </si>
+  <si>
+    <t>DissOrthophos</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>μg/L</t>
+  </si>
+  <si>
+    <t>μS/cm</t>
+  </si>
+  <si>
+    <t>cf/s</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Results are significant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threshold Value </t>
+  </si>
+  <si>
+    <t>Threshold Values Resulting in 5% Chance of Phytoplankton Bloom</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -63,16 +88,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -80,17 +135,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -372,100 +491,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="1.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6.0562757882978803E-2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.32510199966191899</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.145907230574186</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3">
+        <v>11851.6600129946</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3">
+        <v>121.849049059302</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.108933390238636</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.47115097586055998</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.12724209930852801</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3">
+        <v>20332.832931834299</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.0605627578829788</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.325101999661919</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.145907230574186</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="n">
-        <v>11851.6600129946</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="n">
-        <v>121.849049059302</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.108933390238636</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.47115097586056</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.127242099308528</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="n">
-        <v>20332.8329318343</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="n">
+      <c r="C12" s="5">
         <v>15.8208978539882</v>
       </c>
+      <c r="D12" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0bb6ca0c-ccb3-428b-9d5f-a9c60cad6645}" enabled="1" method="Standard" siteId="{fe186a25-7d49-41e6-9941-05d2281d36c1}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>